--- a/final_data_pipeline/output/311513longform_elec_options.xlsx
+++ b/final_data_pipeline/output/311513longform_elec_options.xlsx
@@ -789,7 +789,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="L5">
         <v>8000</v>
@@ -810,10 +810,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R5">
-        <v>1.741590909090909</v>
+        <v>1.782371783972741</v>
       </c>
       <c r="S5">
-        <v>1.89075</v>
+        <v>1.939565227172176</v>
       </c>
       <c r="T5">
         <v>88.16435845162285</v>
@@ -848,7 +848,7 @@
         <v>48</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="L6">
         <v>8000</v>
@@ -863,10 +863,10 @@
         <v>213748.6649440405</v>
       </c>
       <c r="R6">
-        <v>1.741590909090909</v>
+        <v>1.782371783972741</v>
       </c>
       <c r="S6">
-        <v>1.89075</v>
+        <v>1.939565227172176</v>
       </c>
       <c r="T6">
         <v>26.71858311800506</v>
@@ -907,7 +907,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L7">
         <v>8000</v>
@@ -928,10 +928,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R7">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S7">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T7">
         <v>38.58905545096399</v>
@@ -966,7 +966,7 @@
         <v>48</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L8">
         <v>8000</v>
@@ -981,10 +981,10 @@
         <v>93556.61663007623</v>
       </c>
       <c r="R8">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S8">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T8">
         <v>11.69457707875953</v>
@@ -1025,7 +1025,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L9">
         <v>8000</v>
@@ -1046,10 +1046,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R9">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="S9">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="T9">
         <v>44.5681563636969</v>
@@ -1084,7 +1084,7 @@
         <v>48</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L10">
         <v>8000</v>
@@ -1099,10 +1099,10 @@
         <v>108052.5519502842</v>
       </c>
       <c r="R10">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="S10">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="T10">
         <v>13.50656899378552</v>
@@ -1137,7 +1137,7 @@
         <v>49</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L11">
         <v>8000</v>
@@ -1184,7 +1184,7 @@
         <v>49</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="L12">
         <v>8000</v>
@@ -1231,7 +1231,7 @@
         <v>48</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="L13">
         <v>8000</v>
@@ -1246,10 +1246,10 @@
         <v>352052.7507557416</v>
       </c>
       <c r="R13">
-        <v>1.741590909090909</v>
+        <v>1.784885911058073</v>
       </c>
       <c r="S13">
-        <v>1.89075</v>
+        <v>1.942582169301264</v>
       </c>
       <c r="T13">
         <v>44.0065938444677</v>
@@ -1290,7 +1290,7 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="L14">
         <v>8000</v>
@@ -1311,10 +1311,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R14">
-        <v>1.741590909090909</v>
+        <v>1.784885911058073</v>
       </c>
       <c r="S14">
-        <v>1.89075</v>
+        <v>1.942582169301264</v>
       </c>
       <c r="T14">
         <v>145.2102866683866</v>
@@ -1473,7 +1473,7 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="L17">
         <v>8000</v>
@@ -1494,10 +1494,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R17">
-        <v>1.741590909090909</v>
+        <v>1.554711451758341</v>
       </c>
       <c r="S17">
-        <v>1.89075</v>
+        <v>1.669946025515211</v>
       </c>
       <c r="T17">
         <v>60.78420277853312</v>
@@ -1532,7 +1532,7 @@
         <v>48</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="L18">
         <v>8000</v>
@@ -1547,10 +1547,10 @@
         <v>147367.2856217573</v>
       </c>
       <c r="R18">
-        <v>1.741590909090909</v>
+        <v>1.554711451758341</v>
       </c>
       <c r="S18">
-        <v>1.89075</v>
+        <v>1.669946025515211</v>
       </c>
       <c r="T18">
         <v>18.42091070271966</v>
@@ -1921,7 +1921,7 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L25">
         <v>8000</v>
@@ -1942,10 +1942,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R25">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="S25">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="T25">
         <v>61.18327185979957</v>
@@ -1980,7 +1980,7 @@
         <v>48</v>
       </c>
       <c r="K26">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L26">
         <v>8000</v>
@@ -1995,10 +1995,10 @@
         <v>148334.8022559077</v>
       </c>
       <c r="R26">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="S26">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="T26">
         <v>18.54185028198846</v>
@@ -2033,7 +2033,7 @@
         <v>48</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L27">
         <v>8000</v>
@@ -2048,10 +2048,10 @@
         <v>142207.0801410656</v>
       </c>
       <c r="R27">
-        <v>1.741590909090909</v>
+        <v>1.929056920423291</v>
       </c>
       <c r="S27">
-        <v>1.89075</v>
+        <v>2.117059768804106</v>
       </c>
       <c r="T27">
         <v>17.7758850176332</v>
@@ -2086,7 +2086,7 @@
         <v>49</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L28">
         <v>8000</v>
@@ -2139,7 +2139,7 @@
         <v>45</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L29">
         <v>8000</v>
@@ -2160,10 +2160,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R29">
-        <v>1.741590909090909</v>
+        <v>1.929056920423291</v>
       </c>
       <c r="S29">
-        <v>1.89075</v>
+        <v>2.117059768804106</v>
       </c>
       <c r="T29">
         <v>58.655786183263</v>
@@ -2198,7 +2198,7 @@
         <v>48</v>
       </c>
       <c r="K30">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L30">
         <v>8000</v>
@@ -2213,10 +2213,10 @@
         <v>78453.85120309671</v>
       </c>
       <c r="R30">
-        <v>1.741590909090909</v>
+        <v>1.8239809580482</v>
       </c>
       <c r="S30">
-        <v>1.89075</v>
+        <v>1.989608681354817</v>
       </c>
       <c r="T30">
         <v>9.806731400387088</v>
@@ -2257,7 +2257,7 @@
         <v>45</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L31">
         <v>8000</v>
@@ -2278,10 +2278,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R31">
-        <v>1.741590909090909</v>
+        <v>1.8239809580482</v>
       </c>
       <c r="S31">
-        <v>1.89075</v>
+        <v>1.989608681354817</v>
       </c>
       <c r="T31">
         <v>32.35965689512461</v>
@@ -2316,7 +2316,7 @@
         <v>48</v>
       </c>
       <c r="K32">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L32">
         <v>8000</v>
@@ -2331,10 +2331,10 @@
         <v>106751.9041361638</v>
       </c>
       <c r="R32">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="S32">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="T32">
         <v>13.34398801702047</v>
@@ -2375,7 +2375,7 @@
         <v>45</v>
       </c>
       <c r="K33">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L33">
         <v>8000</v>
@@ -2396,10 +2396,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R33">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="S33">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="T33">
         <v>44.03168152707767</v>
@@ -2440,7 +2440,7 @@
         <v>45</v>
       </c>
       <c r="K34">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="L34">
         <v>8000</v>
@@ -2461,10 +2461,10 @@
         <v>2.908846153846154</v>
       </c>
       <c r="R34">
-        <v>1.741590909090909</v>
+        <v>1.554711451758341</v>
       </c>
       <c r="S34">
-        <v>1.89075</v>
+        <v>1.669946025515211</v>
       </c>
       <c r="T34">
         <v>54.10983741284793</v>
@@ -2499,7 +2499,7 @@
         <v>49</v>
       </c>
       <c r="K35">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="L35">
         <v>8000</v>
@@ -2546,7 +2546,7 @@
         <v>48</v>
       </c>
       <c r="K36">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="L36">
         <v>8000</v>
@@ -2561,10 +2561,10 @@
         <v>131185.7275486412</v>
       </c>
       <c r="R36">
-        <v>1.741590909090909</v>
+        <v>1.554711451758341</v>
       </c>
       <c r="S36">
-        <v>1.89075</v>
+        <v>1.669946025515211</v>
       </c>
       <c r="T36">
         <v>16.39821594358015</v>
